--- a/problems/general/3.contract_expiry_tracking/eval/answer_key/1_계약대장_정답.xlsx
+++ b/problems/general/3.contract_expiry_tracking/eval/answer_key/1_계약대장_정답.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="계약대장" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계약대장" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>계약 1건 = data/contracts/ 의 계약서 PDF 1개. 계약번호가 미리 채워져 있음</t>
+          <t>계약 1건 = 데이터/1_계약서/ 의 계약서 PDF 1개. 계약번호가 미리 채워져 있음</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>data/contracts/&lt;계약번호&gt;.pdf — 양식이 제각각인 계약서. 여기서 값을 읽어 옮긴다</t>
+          <t>데이터/1_계약서/&lt;계약번호&gt;.pdf — 양식이 제각각인 계약서. 여기서 값을 읽어 옮긴다</t>
         </is>
       </c>
     </row>
